--- a/EXCEL/class notes/day6 sum&product/Sumproduct Home work.xlsx
+++ b/EXCEL/class notes/day6 sum&product/Sumproduct Home work.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day6 sum&amp;product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F78245-374A-4374-83AA-174371BEE0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAD0C39-0DD6-40A2-875B-F58BB42B869A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7490FD37-6F7C-4F67-B4DB-0E6778C02E62}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{7490FD37-6F7C-4F67-B4DB-0E6778C02E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sumprodcut" sheetId="1" r:id="rId1"/>
@@ -24,18 +24,27 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="58">
   <si>
     <t>Sumproduct</t>
   </si>
@@ -240,6 +249,15 @@
   </si>
   <si>
     <t xml:space="preserve"> =SUMPRODUCT((B7:B16)*(E7:E16))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
   </si>
 </sst>
 </file>
@@ -643,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -803,87 +821,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -1234,7 +1176,126 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B16826-1764-4541-A256-5CC1BC1CB7A8}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77A1D288-A692-4BC6-852C-6451D39993EA}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="T3:X15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" numFmtId="14" showAll="0">
+      <items count="22">
+        <item m="1" x="18"/>
+        <item m="1" x="19"/>
+        <item m="1" x="20"/>
+        <item m="1" x="15"/>
+        <item m="1" x="16"/>
+        <item m="1" x="17"/>
+        <item m="1" x="12"/>
+        <item m="1" x="13"/>
+        <item m="1" x="14"/>
+        <item m="1" x="9"/>
+        <item m="1" x="10"/>
+        <item m="1" x="11"/>
+        <item m="1" x="6"/>
+        <item m="1" x="7"/>
+        <item m="1" x="8"/>
+        <item m="1" x="3"/>
+        <item m="1" x="4"/>
+        <item m="1" x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Mark" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B16826-1764-4541-A256-5CC1BC1CB7A8}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G4:R9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -1341,7 +1402,7 @@
     <dataField name="Sum of Mark" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="15">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
@@ -1349,125 +1410,6 @@
       </pivotArea>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77A1D288-A692-4BC6-852C-6451D39993EA}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="T3:X15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" numFmtId="14" showAll="0">
-      <items count="22">
-        <item m="1" x="18"/>
-        <item m="1" x="19"/>
-        <item m="1" x="20"/>
-        <item m="1" x="15"/>
-        <item m="1" x="16"/>
-        <item m="1" x="17"/>
-        <item m="1" x="12"/>
-        <item m="1" x="13"/>
-        <item m="1" x="14"/>
-        <item m="1" x="9"/>
-        <item m="1" x="10"/>
-        <item m="1" x="11"/>
-        <item m="1" x="6"/>
-        <item m="1" x="7"/>
-        <item m="1" x="8"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Mark" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -1779,13 +1721,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBE1A16-F98D-4ED5-8DB9-F90CFEE4530E}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:Q22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G2" t="s">
         <v>6</v>
       </c>
@@ -1793,12 +1735,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G4" t="s">
         <v>6</v>
       </c>
@@ -1812,7 +1754,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -1832,7 +1774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G6" t="s">
         <v>6</v>
       </c>
@@ -1846,7 +1788,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="79">
         <v>10</v>
       </c>
@@ -1870,7 +1812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="80">
         <v>4</v>
       </c>
@@ -1894,7 +1836,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="80">
         <v>7</v>
       </c>
@@ -1918,7 +1860,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="80">
         <v>2</v>
       </c>
@@ -1942,7 +1884,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="80">
         <v>10</v>
       </c>
@@ -1966,7 +1908,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="80">
         <v>4</v>
       </c>
@@ -1990,7 +1932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="80">
         <v>8</v>
       </c>
@@ -2014,7 +1956,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="80">
         <v>7</v>
       </c>
@@ -2038,7 +1980,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" s="80">
         <v>8</v>
       </c>
@@ -2062,7 +2004,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="81">
         <v>3</v>
       </c>
@@ -2086,7 +2028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
       <c r="I17" s="1">
         <f>SUM(I7:I16)</f>
         <v>122</v>
@@ -2103,17 +2045,16 @@
         <f>SUMPRODUCT((B7:B16&lt;5)*(M7:M16))</f>
         <v>82</v>
       </c>
-      <c r="Q17">
-        <f>SUMIFS(M7:M16,B7:B16,"&lt;5")</f>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="Q17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
       <c r="Q18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C19">
         <f>SUMPRODUCT(B7:B16,E7:E16)</f>
         <v>337</v>
@@ -2130,12 +2071,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
       <c r="K20" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
       <c r="K22">
         <f>SUMPRODUCT(B7:B16,E7:E16)</f>
         <v>337</v>
@@ -2143,12 +2084,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B7:B16">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M16">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$B7&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2160,13 +2101,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C3FB28-1299-4292-B04D-CFD25FE3DBDD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:O25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G2" t="s">
         <v>6</v>
       </c>
@@ -2174,12 +2115,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -2199,7 +2140,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="14">
         <v>6</v>
       </c>
@@ -2223,7 +2164,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="14">
         <v>1</v>
       </c>
@@ -2247,7 +2188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="14">
         <v>9</v>
       </c>
@@ -2271,7 +2212,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="14">
         <v>7</v>
       </c>
@@ -2295,7 +2236,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="14">
         <v>2</v>
       </c>
@@ -2323,7 +2264,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="14">
         <v>4</v>
       </c>
@@ -2350,7 +2291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="14">
         <v>3</v>
       </c>
@@ -2374,7 +2315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="14">
         <v>7</v>
       </c>
@@ -2398,7 +2339,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="55">
         <v>7</v>
       </c>
@@ -2422,7 +2363,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
         <v>9</v>
       </c>
@@ -2446,7 +2387,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
         <v>54</v>
       </c>
@@ -2463,7 +2404,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="77" t="s">
         <v>42</v>
       </c>
@@ -2475,7 +2416,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="21">
         <f>SUMPRODUCT((B7:B16&lt;5)*(M7:M16))</f>
         <v>36</v>
@@ -2500,7 +2441,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>43</v>
       </c>
@@ -2508,7 +2449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>30</v>
       </c>
@@ -2516,7 +2457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22">
         <f>SUMPRODUCT((B7:B16&lt;5)*(M7:M16))</f>
         <v>36</v>
@@ -2525,14 +2466,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23">
         <f>SUMIFS(M7:M16,B7:B16,"&lt;5")</f>
         <v>36</v>
       </c>
-      <c r="D23">
-        <f>SUMPRODUCT(B7:B16,E7:E16)</f>
-        <v>341</v>
+      <c r="D23" t="s">
+        <v>56</v>
       </c>
       <c r="F23">
         <f>SUMIF(B7:B16,"&lt;5",M7:M16)</f>
@@ -2543,7 +2483,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>10</v>
       </c>
@@ -2552,28 +2492,28 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H25" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B7:B16">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+      <formula>5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E7:E16">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$E7&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M16">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$B7&gt;4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B16">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2584,24 +2524,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE12EE84-8B3B-4292-865F-AAA8C3212890}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="8.7265625" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="16" width="5.54296875" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="6.54296875" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="30" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="8.77734375" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="16" width="5.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="6.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="30" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
         <v>11</v>
       </c>
@@ -2618,7 +2558,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="14">
         <v>1001</v>
       </c>
@@ -2634,10 +2574,10 @@
       </c>
       <c r="E2" s="15">
         <f ca="1">TODAY()</f>
-        <v>45756</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
         <v>1002</v>
       </c>
@@ -2653,7 +2593,7 @@
       </c>
       <c r="E3" s="15">
         <f t="shared" ref="E3:E11" ca="1" si="1">TODAY()</f>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="T3" s="7" t="s">
         <v>26</v>
@@ -2662,7 +2602,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1003</v>
       </c>
@@ -2678,7 +2618,7 @@
       </c>
       <c r="E4" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>26</v>
@@ -2702,7 +2642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>1004</v>
       </c>
@@ -2718,7 +2658,7 @@
       </c>
       <c r="E5" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>27</v>
@@ -2759,20 +2699,20 @@
       <c r="T5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="U5" s="83">
+      <c r="U5">
         <v>94</v>
       </c>
-      <c r="V5" s="83">
+      <c r="V5">
         <v>93</v>
       </c>
-      <c r="W5" s="83">
+      <c r="W5">
         <v>24</v>
       </c>
-      <c r="X5" s="83">
+      <c r="X5">
         <v>211</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>1005</v>
       </c>
@@ -2788,61 +2728,61 @@
       </c>
       <c r="E6" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="G6" s="78">
         <v>45756</v>
       </c>
-      <c r="H6" s="83">
+      <c r="H6">
         <v>94</v>
       </c>
-      <c r="I6" s="83">
+      <c r="I6">
         <v>83</v>
       </c>
-      <c r="J6" s="83">
+      <c r="J6">
         <v>30</v>
       </c>
-      <c r="K6" s="83">
+      <c r="K6">
         <v>41</v>
       </c>
-      <c r="L6" s="83">
+      <c r="L6">
         <v>39</v>
       </c>
-      <c r="M6" s="83">
+      <c r="M6">
         <v>12</v>
       </c>
-      <c r="N6" s="83">
+      <c r="N6">
         <v>97</v>
       </c>
-      <c r="O6" s="83">
+      <c r="O6">
         <v>78</v>
       </c>
-      <c r="P6" s="83">
+      <c r="P6">
         <v>30</v>
       </c>
-      <c r="Q6" s="83">
+      <c r="Q6">
         <v>45</v>
       </c>
-      <c r="R6" s="83">
+      <c r="R6">
         <v>549</v>
       </c>
       <c r="T6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="83">
+      <c r="U6">
         <v>45</v>
       </c>
-      <c r="V6" s="83">
+      <c r="V6">
         <v>48</v>
       </c>
-      <c r="W6" s="83">
+      <c r="W6">
         <v>75</v>
       </c>
-      <c r="X6" s="83">
+      <c r="X6">
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>1006</v>
       </c>
@@ -2858,61 +2798,61 @@
       </c>
       <c r="E7" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="G7" s="78">
         <v>45757</v>
       </c>
-      <c r="H7" s="83">
+      <c r="H7">
         <v>93</v>
       </c>
-      <c r="I7" s="83">
+      <c r="I7">
         <v>96</v>
       </c>
-      <c r="J7" s="83">
+      <c r="J7">
         <v>71</v>
       </c>
-      <c r="K7" s="83">
+      <c r="K7">
         <v>80</v>
       </c>
-      <c r="L7" s="83">
+      <c r="L7">
         <v>94</v>
       </c>
-      <c r="M7" s="83">
+      <c r="M7">
         <v>22</v>
       </c>
-      <c r="N7" s="83">
+      <c r="N7">
         <v>98</v>
       </c>
-      <c r="O7" s="83">
+      <c r="O7">
         <v>54</v>
       </c>
-      <c r="P7" s="83">
+      <c r="P7">
         <v>59</v>
       </c>
-      <c r="Q7" s="83">
+      <c r="Q7">
         <v>48</v>
       </c>
-      <c r="R7" s="83">
+      <c r="R7">
         <v>715</v>
       </c>
       <c r="T7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="U7" s="83">
+      <c r="U7">
         <v>83</v>
       </c>
-      <c r="V7" s="83">
+      <c r="V7">
         <v>96</v>
       </c>
-      <c r="W7" s="83">
+      <c r="W7">
         <v>33</v>
       </c>
-      <c r="X7" s="83">
+      <c r="X7">
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>1007</v>
       </c>
@@ -2928,61 +2868,61 @@
       </c>
       <c r="E8" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="G8" s="78">
         <v>45758</v>
       </c>
-      <c r="H8" s="83">
+      <c r="H8">
         <v>24</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8">
         <v>33</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8">
         <v>82</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8">
         <v>69</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8">
         <v>43</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8">
         <v>16</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8">
         <v>41</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8">
         <v>25</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8">
         <v>97</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8">
         <v>75</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8">
         <v>505</v>
       </c>
       <c r="T8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="83">
+      <c r="U8">
         <v>30</v>
       </c>
-      <c r="V8" s="83">
+      <c r="V8">
         <v>71</v>
       </c>
-      <c r="W8" s="83">
+      <c r="W8">
         <v>82</v>
       </c>
-      <c r="X8" s="83">
+      <c r="X8">
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>1008</v>
       </c>
@@ -2998,61 +2938,61 @@
       </c>
       <c r="E9" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="83">
+      <c r="H9">
         <v>211</v>
       </c>
-      <c r="I9" s="83">
+      <c r="I9">
         <v>212</v>
       </c>
-      <c r="J9" s="83">
+      <c r="J9">
         <v>183</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9">
         <v>190</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9">
         <v>176</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9">
         <v>50</v>
       </c>
-      <c r="N9" s="83">
+      <c r="N9">
         <v>236</v>
       </c>
-      <c r="O9" s="83">
+      <c r="O9">
         <v>157</v>
       </c>
-      <c r="P9" s="83">
+      <c r="P9">
         <v>186</v>
       </c>
-      <c r="Q9" s="83">
+      <c r="Q9">
         <v>168</v>
       </c>
-      <c r="R9" s="83">
+      <c r="R9">
         <v>1769</v>
       </c>
       <c r="T9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="U9" s="83">
+      <c r="U9">
         <v>41</v>
       </c>
-      <c r="V9" s="83">
+      <c r="V9">
         <v>80</v>
       </c>
-      <c r="W9" s="83">
+      <c r="W9">
         <v>69</v>
       </c>
-      <c r="X9" s="83">
+      <c r="X9">
         <v>190</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>1009</v>
       </c>
@@ -3068,25 +3008,25 @@
       </c>
       <c r="E10" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="T10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="U10" s="83">
+      <c r="U10">
         <v>39</v>
       </c>
-      <c r="V10" s="83">
+      <c r="V10">
         <v>94</v>
       </c>
-      <c r="W10" s="83">
+      <c r="W10">
         <v>43</v>
       </c>
-      <c r="X10" s="83">
+      <c r="X10">
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>1010</v>
       </c>
@@ -3102,25 +3042,25 @@
       </c>
       <c r="E11" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="T11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="U11" s="83">
+      <c r="U11">
         <v>12</v>
       </c>
-      <c r="V11" s="83">
+      <c r="V11">
         <v>22</v>
       </c>
-      <c r="W11" s="83">
+      <c r="W11">
         <v>16</v>
       </c>
-      <c r="X11" s="83">
+      <c r="X11">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>1001</v>
       </c>
@@ -3136,7 +3076,7 @@
       </c>
       <c r="E12" s="56">
         <f ca="1">E2+1</f>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>27</v>
@@ -3187,20 +3127,20 @@
       <c r="T12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="U12" s="83">
+      <c r="U12">
         <v>97</v>
       </c>
-      <c r="V12" s="83">
+      <c r="V12">
         <v>98</v>
       </c>
-      <c r="W12" s="83">
+      <c r="W12">
         <v>41</v>
       </c>
-      <c r="X12" s="83">
+      <c r="X12">
         <v>236</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>1002</v>
       </c>
@@ -3216,11 +3156,11 @@
       </c>
       <c r="E13" s="56">
         <f t="shared" ref="E13:E31" ca="1" si="3">E3+1</f>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G13" s="8">
         <f ca="1">TODAY()</f>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="H13" s="1">
         <f ca="1">SUMPRODUCT(($B$2:$B$31=H$12)*($E$2:$E$31=$G13)*($C$2:$C$31))</f>
@@ -3269,20 +3209,20 @@
       <c r="T13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="U13" s="83">
+      <c r="U13">
         <v>78</v>
       </c>
-      <c r="V13" s="83">
+      <c r="V13">
         <v>54</v>
       </c>
-      <c r="W13" s="83">
+      <c r="W13">
         <v>25</v>
       </c>
-      <c r="X13" s="83">
+      <c r="X13">
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>1003</v>
       </c>
@@ -3298,11 +3238,11 @@
       </c>
       <c r="E14" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G14" s="8">
         <f ca="1">G13+1</f>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" ref="H14:Q15" ca="1" si="5">SUMPRODUCT(($B$2:$B$31=H$12)*($E$2:$E$31=$G14)*($C$2:$C$31))</f>
@@ -3351,20 +3291,20 @@
       <c r="T14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="83">
+      <c r="U14">
         <v>30</v>
       </c>
-      <c r="V14" s="83">
+      <c r="V14">
         <v>59</v>
       </c>
-      <c r="W14" s="83">
+      <c r="W14">
         <v>97</v>
       </c>
-      <c r="X14" s="83">
+      <c r="X14">
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>1004</v>
       </c>
@@ -3380,11 +3320,11 @@
       </c>
       <c r="E15" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G15" s="8">
         <f ca="1">G14+1</f>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" ca="1" si="5"/>
@@ -3433,20 +3373,20 @@
       <c r="T15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="U15" s="83">
+      <c r="U15">
         <v>549</v>
       </c>
-      <c r="V15" s="83">
+      <c r="V15">
         <v>715</v>
       </c>
-      <c r="W15" s="83">
+      <c r="W15">
         <v>505</v>
       </c>
-      <c r="X15" s="83">
+      <c r="X15">
         <v>1769</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>1005</v>
       </c>
@@ -3462,7 +3402,7 @@
       </c>
       <c r="E16" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>28</v>
@@ -3512,7 +3452,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
         <v>1006</v>
       </c>
@@ -3528,28 +3468,28 @@
       </c>
       <c r="E17" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="T17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="U17" s="12">
         <f ca="1">TODAY()</f>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="V17" s="12">
         <f ca="1">U17+1</f>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="W17" s="12">
         <f ca="1">V17+1</f>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="X17" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>1007</v>
       </c>
@@ -3565,7 +3505,7 @@
       </c>
       <c r="E18" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="T18" s="11" t="s">
         <v>16</v>
@@ -3587,7 +3527,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>1008</v>
       </c>
@@ -3603,7 +3543,7 @@
       </c>
       <c r="E19" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>27</v>
@@ -3671,7 +3611,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>1009</v>
       </c>
@@ -3687,11 +3627,11 @@
       </c>
       <c r="E20" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G20" s="8">
         <f ca="1">TODAY()</f>
-        <v>45756</v>
+        <v>45924</v>
       </c>
       <c r="H20" s="58">
         <f ca="1">SUMPRODUCT(($B$2:$B$31=H$19)*($E$2:$E$31=$G20)*($C$2:$C$31))</f>
@@ -3757,7 +3697,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
         <v>1010</v>
       </c>
@@ -3773,11 +3713,11 @@
       </c>
       <c r="E21" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="G21" s="8">
         <f ca="1">G20+1</f>
-        <v>45757</v>
+        <v>45925</v>
       </c>
       <c r="H21" s="58">
         <f t="shared" ref="H21:Q22" ca="1" si="13">SUMPRODUCT(($B$2:$B$31=H$19)*($E$2:$E$31=$G21)*($C$2:$C$31))</f>
@@ -3843,7 +3783,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>1001</v>
       </c>
@@ -3859,11 +3799,11 @@
       </c>
       <c r="E22" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="G22" s="8">
         <f ca="1">G21+1</f>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="H22" s="58">
         <f t="shared" ca="1" si="13"/>
@@ -3929,7 +3869,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>1002</v>
       </c>
@@ -3945,7 +3885,7 @@
       </c>
       <c r="E23" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>28</v>
@@ -4014,7 +3954,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>1003</v>
       </c>
@@ -4030,7 +3970,7 @@
       </c>
       <c r="E24" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="T24" s="11" t="s">
         <v>21</v>
@@ -4052,7 +3992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
         <v>1004</v>
       </c>
@@ -4068,7 +4008,7 @@
       </c>
       <c r="E25" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="T25" s="11" t="s">
         <v>22</v>
@@ -4090,7 +4030,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>1005</v>
       </c>
@@ -4106,7 +4046,7 @@
       </c>
       <c r="E26" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="T26" s="11" t="s">
         <v>23</v>
@@ -4128,7 +4068,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>1006</v>
       </c>
@@ -4144,7 +4084,7 @@
       </c>
       <c r="E27" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="T27" s="11" t="s">
         <v>24</v>
@@ -4166,7 +4106,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>1007</v>
       </c>
@@ -4182,7 +4122,7 @@
       </c>
       <c r="E28" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
       <c r="T28" s="13" t="s">
         <v>28</v>
@@ -4204,7 +4144,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
         <v>1008</v>
       </c>
@@ -4220,10 +4160,10 @@
       </c>
       <c r="E29" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
         <v>1009</v>
       </c>
@@ -4239,10 +4179,10 @@
       </c>
       <c r="E30" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
         <v>1010</v>
       </c>
@@ -4258,7 +4198,7 @@
       </c>
       <c r="E31" s="15">
         <f t="shared" ca="1" si="3"/>
-        <v>45758</v>
+        <v>45926</v>
       </c>
     </row>
   </sheetData>
@@ -4272,13 +4212,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5FFD96-93D8-4E30-A985-E6653F99632B}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="51" t="s">
         <v>11</v>
       </c>
@@ -4301,7 +4241,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="24">
         <v>1001</v>
       </c>
@@ -4324,7 +4264,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="27">
         <v>1002</v>
       </c>
@@ -4347,7 +4287,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="27">
         <v>1003</v>
       </c>
@@ -4370,7 +4310,7 @@
         <v>31</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M4" t="b">
         <f>K1=K2</f>
@@ -4380,10 +4320,10 @@
         <v>31</v>
       </c>
       <c r="P4" s="61" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="27">
         <v>1004</v>
       </c>
@@ -4406,7 +4346,7 @@
         <v>11</v>
       </c>
       <c r="K5" s="18">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>11</v>
@@ -4415,7 +4355,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <v>1005</v>
       </c>
@@ -4439,7 +4379,7 @@
       </c>
       <c r="K6" s="14" t="str">
         <f>INDEX($B$2:$B$11,MATCH(K5,A2:A11,0))</f>
-        <v>Ram4</v>
+        <v>Ram1</v>
       </c>
       <c r="O6" s="14" t="s">
         <v>12</v>
@@ -4449,7 +4389,7 @@
         <v>Ram5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="27">
         <v>1006</v>
       </c>
@@ -4473,25 +4413,24 @@
       </c>
       <c r="K7" s="16">
         <f>SUMPRODUCT(($F$2:$F$21=$K$4)*($A$2:$A$21=$K$5)*($C$1:$E$1=$J7)*($C$2:$E$21))</f>
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="L7">
         <f>SUMPRODUCT(($A$2:$A$21=$K$5)*($F$2:$F$21=$K$4)*($C$1:$E$1=$J7)*($C$2:$E$21))</f>
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="M7">
         <f>SUMIFS(C$2:C$21,$A$2:$A$21,$K$5,$F$2:$F$21,$K$4)</f>
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="O7" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="16">
-        <f>SUMPRODUCT(($A$2:$A$21=$P$5)*($F$2:$F$21=$P$4)*($C$1:$E$1=$O7)*($C$2:$E$21))</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P7" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
         <v>1007</v>
       </c>
@@ -4515,25 +4454,25 @@
       </c>
       <c r="K8" s="16">
         <f t="shared" ref="K8:K9" si="0">SUMPRODUCT(($F$2:$F$21=$K$4)*($A$2:$A$21=$K$5)*($C$1:$E$1=$J8)*($C$2:$E$21))</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L8">
         <f t="shared" ref="L8:L9" si="1">SUMPRODUCT(($A$2:$A$21=$K$5)*($F$2:$F$21=$K$4)*($C$1:$E$1=$J8)*($C$2:$E$21))</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M8">
         <f>SUMIFS(D$2:D$21,$A$2:$A$21,$K$5,$F$2:$F$21,$K$4)</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="O8" s="15" t="s">
         <v>33</v>
       </c>
       <c r="P8" s="16">
         <f t="shared" ref="P8:P9" si="2">SUMPRODUCT(($A$2:$A$21=$P$5)*($F$2:$F$21=$P$4)*($C$1:$E$1=$O8)*($C$2:$E$21))</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
         <v>1008</v>
       </c>
@@ -4557,25 +4496,25 @@
       </c>
       <c r="K9" s="16">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="L9">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="M9">
         <f>SUMIFS(E$2:E$21,$A$2:$A$21,$K$5,$F$2:$F$21,$K$4)</f>
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="O9" s="15" t="s">
         <v>34</v>
       </c>
       <c r="P9" s="16">
         <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
         <v>1009</v>
       </c>
@@ -4595,7 +4534,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="30">
         <v>1010</v>
       </c>
@@ -4614,8 +4553,11 @@
       <c r="F11" s="32" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="33">
         <v>1001</v>
       </c>
@@ -4641,7 +4583,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>1002</v>
       </c>
@@ -4670,7 +4612,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>1003</v>
       </c>
@@ -4700,7 +4642,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>1004</v>
       </c>
@@ -4727,7 +4669,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
         <v>1005</v>
       </c>
@@ -4754,7 +4696,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>1006</v>
       </c>
@@ -4781,7 +4723,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>1007</v>
       </c>
@@ -4801,7 +4743,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>1008</v>
       </c>
@@ -4824,7 +4766,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>1009</v>
       </c>
@@ -4844,7 +4786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="37">
         <v>1010</v>
       </c>
@@ -4886,13 +4828,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EE1EE6-187B-4103-95A0-91BEC27D13AF}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="51" t="s">
         <v>11</v>
       </c>
@@ -4924,7 +4866,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="62">
         <v>1001</v>
       </c>
@@ -4948,9 +4890,9 @@
         <f>AND(C2&gt;34,D2&gt;34,E2&gt;34)</f>
         <v>1</v>
       </c>
-      <c r="H2" s="73" t="str">
-        <f>IF(AND(C2&gt;34,D2&gt;34,E2&gt;34),"Pass","Fail")</f>
-        <v>Pass</v>
+      <c r="H2" s="73">
+        <f>M14</f>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <f>OR(C2&gt;34,D2&gt;34,E2&gt;34)</f>
@@ -4961,7 +4903,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="64">
         <v>1002</v>
       </c>
@@ -4998,7 +4940,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="64">
         <v>1003</v>
       </c>
@@ -5035,7 +4977,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="64">
         <v>1004</v>
       </c>
@@ -5072,7 +5014,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="66">
         <v>1005</v>
       </c>
@@ -5109,7 +5051,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="64">
         <v>1006</v>
       </c>
@@ -5146,7 +5088,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="64">
         <v>1007</v>
       </c>
@@ -5183,7 +5125,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="64">
         <v>1008</v>
       </c>
@@ -5220,7 +5162,7 @@
         <v>All Fail</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="64">
         <v>1009</v>
       </c>
@@ -5257,7 +5199,7 @@
         <v>All Fail</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67">
         <v>1010</v>
       </c>
@@ -5294,7 +5236,7 @@
         <v>1 or more pass</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
         <v>46</v>
       </c>
